--- a/Incubations/PR wetlands supplies.xlsx
+++ b/Incubations/PR wetlands supplies.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carla López Lloreda\Dropbox\Grad school\Research\Humedales Puerto Rico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carla López Lloreda\Dropbox\Grad school\Research\Humedales Puerto Rico\PR-wetlands\incubations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346BF8D4-3E6F-4BE7-B9FB-04020D469A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BB5F992-FE3F-4ECB-9614-206D0B33CC70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AD1FB43F-0597-4855-855B-8033E620BFE8}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>Expense</t>
   </si>
@@ -160,6 +160,39 @@
   </si>
   <si>
     <t>Sediment sampler?</t>
+  </si>
+  <si>
+    <t>~200</t>
+  </si>
+  <si>
+    <t>DOC</t>
+  </si>
+  <si>
+    <t>1l bottles</t>
+  </si>
+  <si>
+    <t>miniDOTs</t>
+  </si>
+  <si>
+    <t>HOBO cond</t>
+  </si>
+  <si>
+    <t>HOBO cables</t>
+  </si>
+  <si>
+    <t>minidot cable</t>
+  </si>
+  <si>
+    <t>crimper</t>
+  </si>
+  <si>
+    <t>decapper</t>
+  </si>
+  <si>
+    <t>250ml HDPE</t>
+  </si>
+  <si>
+    <t>60 ml HDPE</t>
   </si>
 </sst>
 </file>
@@ -186,12 +219,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -206,10 +245,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -524,108 +564,180 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3F09D32-CDBB-4D52-AFB2-77A9B83E4A40}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.77734375" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" customWidth="1"/>
+    <col min="1" max="2" width="20.77734375" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
